--- a/Issues Log.xlsx
+++ b/Issues Log.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://klickconsultancy-my.sharepoint.com/personal/chris_klickconsultancy_com/Documents/Clients/Aireka/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MattTaylor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{B2568209-2659-4A02-9E01-FA5FABA7FD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4619751B-4FD6-42AA-B326-0944E8960B5A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A60C97C-6ED4-4D74-8FDC-9CFFE6B38535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AB3A7E7A-57A9-4EA1-B437-D20230C178A4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{AB3A7E7A-57A9-4EA1-B437-D20230C178A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing functionality - issues" sheetId="1" r:id="rId1"/>
+    <sheet name="TODO" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
   <si>
     <t>Superadmin</t>
   </si>
@@ -171,13 +172,79 @@
   </si>
   <si>
     <t>What I realized was that for something I didn't know a date for ie future date I could just put today's date and then go back to it. But whether there is a filter to show bookings with no date, past dates, current or future???</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>PRIORITY</t>
+  </si>
+  <si>
+    <t>AREA</t>
+  </si>
+  <si>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>ALLOCATED TO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARGET DATE </t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Landing page</t>
+  </si>
+  <si>
+    <t>Site marketing landing page</t>
+  </si>
+  <si>
+    <t>Idea</t>
+  </si>
+  <si>
+    <t>Create a landing page for the site that explains the core benefits of the app and who can use it, what the subscriptions are and what you get for your money. Should be outcome and benefit focused.</t>
+  </si>
+  <si>
+    <t>Job management</t>
+  </si>
+  <si>
+    <t>End to end process flow</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Matt</t>
+  </si>
+  <si>
+    <t>Build in the concept of a process flow from job creation and quoting through delivery, completion and invoice.</t>
+  </si>
+  <si>
+    <t>Bug fixing</t>
+  </si>
+  <si>
+    <t>Russell initial feedback bug fixing</t>
+  </si>
+  <si>
+    <t>See feedback from "Testing functionality - issues" tab.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,13 +260,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -214,14 +295,115 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -785,4 +967,285 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D894769C-8D2E-4ABF-8AF2-029E96631A9F}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="14.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="40.77734375" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46129</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46122</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46122</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"LOW"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"MEDIUM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"HIGH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{DAD80926-3D85-480E-98E6-090E120B4F8D}">
+      <formula1>"Chris,Matt,Russell"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{5730F299-231E-4845-9C4D-F384122A2D15}">
+      <formula1>"Idea,Scoping,In Progress,Testing,Complete,Live"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{2DD42007-15CF-4677-B836-A25CE7B36FDF}">
+      <formula1>"LOW,MEDIUM,HIGH"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{40170256-501D-4618-AF0C-DCCE4D12F8D6}">
+      <formula1>"Bug fixing,Landing page,Login Page,Dashboard,Job page,Quote,Invoice,User management,Job management,File management,Security,Database,Infrastructure"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>